--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/91.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/91.xlsx
@@ -426,13 +426,13 @@
         <v>-6.840616267080263</v>
       </c>
       <c r="E2">
-        <v>-9.364066670774513</v>
+        <v>-9.033365799416369</v>
       </c>
       <c r="F2">
-        <v>1.003775127911966</v>
+        <v>0.9884226827676963</v>
       </c>
       <c r="G2">
-        <v>-14.77451896878784</v>
+        <v>-14.00141720063846</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.999928672701694</v>
       </c>
       <c r="E3">
-        <v>-9.088001838318913</v>
+        <v>-8.423285252629011</v>
       </c>
       <c r="F3">
-        <v>1.380456412487408</v>
+        <v>1.057963209514643</v>
       </c>
       <c r="G3">
-        <v>-15.11637252226406</v>
+        <v>-14.51540256942909</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.076273014812766</v>
       </c>
       <c r="E4">
-        <v>-10.46881507578974</v>
+        <v>-10.62372058617012</v>
       </c>
       <c r="F4">
-        <v>1.312244615003516</v>
+        <v>1.115540421776359</v>
       </c>
       <c r="G4">
-        <v>-13.59361261420164</v>
+        <v>-12.80322152197342</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.193582303454478</v>
       </c>
       <c r="E5">
-        <v>-11.24413511064298</v>
+        <v>-10.35029132558699</v>
       </c>
       <c r="F5">
-        <v>1.453698059958736</v>
+        <v>1.570778270875343</v>
       </c>
       <c r="G5">
-        <v>-13.52035686250865</v>
+        <v>-12.59944751239466</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.358356439131842</v>
       </c>
       <c r="E6">
-        <v>-12.42594908632075</v>
+        <v>-11.88762673865893</v>
       </c>
       <c r="F6">
-        <v>1.710302762025559</v>
+        <v>1.394145966420467</v>
       </c>
       <c r="G6">
-        <v>-12.57723706237169</v>
+        <v>-12.24707966628571</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.602689755102828</v>
       </c>
       <c r="E7">
-        <v>-11.93185181581784</v>
+        <v>-11.833348449203</v>
       </c>
       <c r="F7">
-        <v>1.848572958090746</v>
+        <v>1.406543216326527</v>
       </c>
       <c r="G7">
-        <v>-12.26409587035757</v>
+        <v>-12.46103360339773</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.922537148415183</v>
       </c>
       <c r="E8">
-        <v>-13.54435536894311</v>
+        <v>-13.21528021975372</v>
       </c>
       <c r="F8">
-        <v>1.815490925223131</v>
+        <v>1.657380061449319</v>
       </c>
       <c r="G8">
-        <v>-12.34657480192297</v>
+        <v>-11.33308770107603</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.32354594143209</v>
       </c>
       <c r="E9">
-        <v>-14.86742150586813</v>
+        <v>-13.94834053516738</v>
       </c>
       <c r="F9">
-        <v>1.742075070101105</v>
+        <v>1.942716356234044</v>
       </c>
       <c r="G9">
-        <v>-11.36787491360269</v>
+        <v>-10.8161261518456</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.7829757195271617</v>
       </c>
       <c r="E10">
-        <v>-15.28520946086778</v>
+        <v>-13.97808355244976</v>
       </c>
       <c r="F10">
-        <v>1.94221432145885</v>
+        <v>2.073375261669629</v>
       </c>
       <c r="G10">
-        <v>-9.74960080091399</v>
+        <v>-9.174588835652438</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.2839762655500697</v>
       </c>
       <c r="E11">
-        <v>-16.28121109106281</v>
+        <v>-16.47994317288943</v>
       </c>
       <c r="F11">
-        <v>2.120610874303527</v>
+        <v>2.5291040596024</v>
       </c>
       <c r="G11">
-        <v>-9.730224177872635</v>
+        <v>-9.201006989055823</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.1970940265853964</v>
       </c>
       <c r="E12">
-        <v>-16.27945857162184</v>
+        <v>-16.60609740179511</v>
       </c>
       <c r="F12">
-        <v>2.441596389244793</v>
+        <v>2.530089124681803</v>
       </c>
       <c r="G12">
-        <v>-9.65271106461614</v>
+        <v>-9.174856989841119</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.6902944246456665</v>
       </c>
       <c r="E13">
-        <v>-17.1754035686174</v>
+        <v>-16.53703817317814</v>
       </c>
       <c r="F13">
-        <v>2.367391848576878</v>
+        <v>2.695611732139873</v>
       </c>
       <c r="G13">
-        <v>-8.537550489167101</v>
+        <v>-8.167825452795757</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.212961599751653</v>
       </c>
       <c r="E14">
-        <v>-19.12271079055176</v>
+        <v>-18.79309675295546</v>
       </c>
       <c r="F14">
-        <v>2.596585768659275</v>
+        <v>2.634205118974624</v>
       </c>
       <c r="G14">
-        <v>-8.302620935518261</v>
+        <v>-7.580878970865132</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.78763068004801</v>
       </c>
       <c r="E15">
-        <v>-19.19113603280766</v>
+        <v>-19.59276639254795</v>
       </c>
       <c r="F15">
-        <v>2.779245657828314</v>
+        <v>2.623584787105687</v>
       </c>
       <c r="G15">
-        <v>-7.061821846308342</v>
+        <v>-6.561101833493574</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.4264037078648</v>
       </c>
       <c r="E16">
-        <v>-19.95921503772264</v>
+        <v>-20.09542247892535</v>
       </c>
       <c r="F16">
-        <v>3.105745636767142</v>
+        <v>2.914251836001781</v>
       </c>
       <c r="G16">
-        <v>-6.880294702753485</v>
+        <v>-5.72945968857326</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.124741106225593</v>
       </c>
       <c r="E17">
-        <v>-20.99161201351732</v>
+        <v>-21.68194617666861</v>
       </c>
       <c r="F17">
-        <v>3.169046362207257</v>
+        <v>3.202163236605011</v>
       </c>
       <c r="G17">
-        <v>-6.817447306235961</v>
+        <v>-6.052145183377101</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.87454970831098</v>
       </c>
       <c r="E18">
-        <v>-21.93794081232222</v>
+        <v>-22.61583072890043</v>
       </c>
       <c r="F18">
-        <v>2.975625191342806</v>
+        <v>3.257358555169906</v>
       </c>
       <c r="G18">
-        <v>-5.487991807484359</v>
+        <v>-6.214825391176888</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.645992884743519</v>
       </c>
       <c r="E19">
-        <v>-23.34601546331923</v>
+        <v>-21.97054129670344</v>
       </c>
       <c r="F19">
-        <v>3.284265718673223</v>
+        <v>3.853677678333983</v>
       </c>
       <c r="G19">
-        <v>-5.703955245738714</v>
+        <v>-5.382570795331807</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.402639963970378</v>
       </c>
       <c r="E20">
-        <v>-23.14983744083294</v>
+        <v>-23.95743643841285</v>
       </c>
       <c r="F20">
-        <v>3.491428705765942</v>
+        <v>4.176400518664487</v>
       </c>
       <c r="G20">
-        <v>-5.589436854444246</v>
+        <v>-5.19864019571544</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.104744768775885</v>
       </c>
       <c r="E21">
-        <v>-23.5444305519653</v>
+        <v>-22.73218081157951</v>
       </c>
       <c r="F21">
-        <v>3.834196511868163</v>
+        <v>3.926086296493791</v>
       </c>
       <c r="G21">
-        <v>-5.405694955923616</v>
+        <v>-4.862331806017497</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.707414654456091</v>
       </c>
       <c r="E22">
-        <v>-25.25648354920119</v>
+        <v>-24.59715131910641</v>
       </c>
       <c r="F22">
-        <v>3.744386133109507</v>
+        <v>4.149246297038363</v>
       </c>
       <c r="G22">
-        <v>-4.671624519682241</v>
+        <v>-3.927321187178979</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.17967236685963</v>
       </c>
       <c r="E23">
-        <v>-24.60069711425441</v>
+        <v>-25.92325606209057</v>
       </c>
       <c r="F23">
-        <v>3.794340968800214</v>
+        <v>3.712175138495384</v>
       </c>
       <c r="G23">
-        <v>-4.405039529586889</v>
+        <v>-3.811700384219932</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.499548255373989</v>
       </c>
       <c r="E24">
-        <v>-24.85431430105399</v>
+        <v>-24.96269879795357</v>
       </c>
       <c r="F24">
-        <v>3.675358727079164</v>
+        <v>3.719862447008927</v>
       </c>
       <c r="G24">
-        <v>-4.205800967396931</v>
+        <v>-4.287462194214134</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.658934519577485</v>
       </c>
       <c r="E25">
-        <v>-24.95989114406882</v>
+        <v>-24.66996012420173</v>
       </c>
       <c r="F25">
-        <v>3.844105759781067</v>
+        <v>4.097581058958982</v>
       </c>
       <c r="G25">
-        <v>-4.571626181123015</v>
+        <v>-4.653969380321308</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>7.667236542013574</v>
       </c>
       <c r="E26">
-        <v>-24.89141608859883</v>
+        <v>-26.69143922190772</v>
       </c>
       <c r="F26">
-        <v>3.649309932182015</v>
+        <v>3.49945809475722</v>
       </c>
       <c r="G26">
-        <v>-4.510281772280321</v>
+        <v>-3.513377194039588</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>7.542554388350545</v>
       </c>
       <c r="E27">
-        <v>-25.46587565884186</v>
+        <v>-25.17760658893559</v>
       </c>
       <c r="F27">
-        <v>3.45424804198917</v>
+        <v>3.766955526110435</v>
       </c>
       <c r="G27">
-        <v>-4.102819827306823</v>
+        <v>-3.527761514407721</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>7.313827684980082</v>
       </c>
       <c r="E28">
-        <v>-25.08420228405338</v>
+        <v>-26.0159629819756</v>
       </c>
       <c r="F28">
-        <v>3.562583028840721</v>
+        <v>3.573795666722032</v>
       </c>
       <c r="G28">
-        <v>-3.979654291063778</v>
+        <v>-3.677173055686108</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>7.009251325286242</v>
       </c>
       <c r="E29">
-        <v>-24.94386487455567</v>
+        <v>-25.46981090275452</v>
       </c>
       <c r="F29">
-        <v>3.113961903056442</v>
+        <v>4.015896675252447</v>
       </c>
       <c r="G29">
-        <v>-4.711930411622868</v>
+        <v>-3.896145779835662</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.656695531581192</v>
       </c>
       <c r="E30">
-        <v>-25.10493363806049</v>
+        <v>-25.10386038972067</v>
       </c>
       <c r="F30">
-        <v>3.519841973594841</v>
+        <v>3.7752810681079</v>
       </c>
       <c r="G30">
-        <v>-3.951173667789428</v>
+        <v>-3.789221780008281</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.278881881495811</v>
       </c>
       <c r="E31">
-        <v>-24.97259804213434</v>
+        <v>-25.46963882074223</v>
       </c>
       <c r="F31">
-        <v>3.546446649268308</v>
+        <v>3.748932952792734</v>
       </c>
       <c r="G31">
-        <v>-3.810409271459617</v>
+        <v>-4.607972660598674</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.887603049152851</v>
       </c>
       <c r="E32">
-        <v>-24.92479547050937</v>
+        <v>-24.55543048807374</v>
       </c>
       <c r="F32">
-        <v>3.116801487762825</v>
+        <v>3.280629529891374</v>
       </c>
       <c r="G32">
-        <v>-4.722014333335488</v>
+        <v>-3.307093790942061</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.490446508747746</v>
       </c>
       <c r="E33">
-        <v>-24.06258760487096</v>
+        <v>-25.11966929248145</v>
       </c>
       <c r="F33">
-        <v>3.06400548365982</v>
+        <v>3.823162832755296</v>
       </c>
       <c r="G33">
-        <v>-4.581624028651615</v>
+        <v>-3.75415979220186</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.083314581035471</v>
       </c>
       <c r="E34">
-        <v>-24.58942121397531</v>
+        <v>-23.45514715843007</v>
       </c>
       <c r="F34">
-        <v>3.28146414290881</v>
+        <v>3.488668306355331</v>
       </c>
       <c r="G34">
-        <v>-4.687150978261423</v>
+        <v>-3.943251532313952</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.661044385592382</v>
       </c>
       <c r="E35">
-        <v>-22.51295738486819</v>
+        <v>-23.30202586680872</v>
       </c>
       <c r="F35">
-        <v>3.38635456939428</v>
+        <v>3.534046231950417</v>
       </c>
       <c r="G35">
-        <v>-4.156735371959393</v>
+        <v>-4.510417504647431</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.221248408747998</v>
       </c>
       <c r="E36">
-        <v>-23.38885029895778</v>
+        <v>-23.02943890239101</v>
       </c>
       <c r="F36">
-        <v>3.324173524036381</v>
+        <v>3.677374784709518</v>
       </c>
       <c r="G36">
-        <v>-5.230302253253029</v>
+        <v>-4.160784169153922</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.758551255690122</v>
       </c>
       <c r="E37">
-        <v>-22.42338416899647</v>
+        <v>-21.66061706409249</v>
       </c>
       <c r="F37">
-        <v>3.349373452562854</v>
+        <v>3.579455831663812</v>
       </c>
       <c r="G37">
-        <v>-4.709394533739786</v>
+        <v>-3.892828613205312</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.280174502369857</v>
       </c>
       <c r="E38">
-        <v>-21.35086944196783</v>
+        <v>-20.97914512457421</v>
       </c>
       <c r="F38">
-        <v>3.498802440508228</v>
+        <v>3.895237288966945</v>
       </c>
       <c r="G38">
-        <v>-4.635354182753986</v>
+        <v>-4.478550193286407</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.791821965507552</v>
       </c>
       <c r="E39">
-        <v>-20.91052515793598</v>
+        <v>-21.69876040065909</v>
       </c>
       <c r="F39">
-        <v>3.455611612782363</v>
+        <v>4.201036647885064</v>
       </c>
       <c r="G39">
-        <v>-5.254763874242704</v>
+        <v>-4.36084043609208</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.301004023290015</v>
       </c>
       <c r="E40">
-        <v>-20.12496624335139</v>
+        <v>-21.01224826957028</v>
       </c>
       <c r="F40">
-        <v>3.307514521511874</v>
+        <v>3.865191220339228</v>
       </c>
       <c r="G40">
-        <v>-4.704928607807309</v>
+        <v>-3.883522669694421</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.821208815015748</v>
       </c>
       <c r="E41">
-        <v>-19.26471467848429</v>
+        <v>-20.33086237105814</v>
       </c>
       <c r="F41">
-        <v>3.808359933563684</v>
+        <v>4.002617301151487</v>
       </c>
       <c r="G41">
-        <v>-4.710771720684123</v>
+        <v>-5.218069787485422</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.359515047018727</v>
       </c>
       <c r="E42">
-        <v>-19.67198751683813</v>
+        <v>-20.31272130418341</v>
       </c>
       <c r="F42">
-        <v>3.858278344018335</v>
+        <v>3.833230451259745</v>
       </c>
       <c r="G42">
-        <v>-5.045395042702576</v>
+        <v>-4.671432508040963</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.9259538924052061</v>
       </c>
       <c r="E43">
-        <v>-18.66752669719677</v>
+        <v>-18.73926678242628</v>
       </c>
       <c r="F43">
-        <v>3.704920181696756</v>
+        <v>4.110451836933758</v>
       </c>
       <c r="G43">
-        <v>-5.588589354786192</v>
+        <v>-5.435281301408083</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.5263984684559518</v>
       </c>
       <c r="E44">
-        <v>-17.98134967318452</v>
+        <v>-18.6235008728942</v>
       </c>
       <c r="F44">
-        <v>4.034370604756047</v>
+        <v>3.593093123301661</v>
       </c>
       <c r="G44">
-        <v>-5.338318733108369</v>
+        <v>-5.202427459812365</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.1599616877647125</v>
       </c>
       <c r="E45">
-        <v>-18.35620316611745</v>
+        <v>-18.35954970840912</v>
       </c>
       <c r="F45">
-        <v>3.760170929968692</v>
+        <v>3.767924754130684</v>
       </c>
       <c r="G45">
-        <v>-6.027206843829771</v>
+        <v>-4.88616442335471</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.1706492580888507</v>
       </c>
       <c r="E46">
-        <v>-16.95364419646179</v>
+        <v>-17.3767802792645</v>
       </c>
       <c r="F46">
-        <v>3.79548123705933</v>
+        <v>3.878603625737085</v>
       </c>
       <c r="G46">
-        <v>-5.629971174027082</v>
+        <v>-5.462384737738097</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.4695703152814918</v>
       </c>
       <c r="E47">
-        <v>-16.87770168735316</v>
+        <v>-16.64691253802624</v>
       </c>
       <c r="F47">
-        <v>4.03212649347387</v>
+        <v>3.816609457677208</v>
       </c>
       <c r="G47">
-        <v>-5.767835532464492</v>
+        <v>-5.887339605341102</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7398531678189869</v>
       </c>
       <c r="E48">
-        <v>-15.21093343019397</v>
+        <v>-15.66032107681915</v>
       </c>
       <c r="F48">
-        <v>4.324123855338933</v>
+        <v>4.09851227803726</v>
       </c>
       <c r="G48">
-        <v>-5.971242071488391</v>
+        <v>-6.036449886975416</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.9812993709442628</v>
       </c>
       <c r="E49">
-        <v>-14.66019853527713</v>
+        <v>-15.14005828349992</v>
       </c>
       <c r="F49">
-        <v>3.899980488183687</v>
+        <v>3.809774182946171</v>
       </c>
       <c r="G49">
-        <v>-6.548849504452732</v>
+        <v>-5.707133369456415</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.196495470216687</v>
       </c>
       <c r="E50">
-        <v>-14.66733541031322</v>
+        <v>-15.0826598754527</v>
       </c>
       <c r="F50">
-        <v>4.096634002821549</v>
+        <v>4.031420160635584</v>
       </c>
       <c r="G50">
-        <v>-6.762028773908561</v>
+        <v>-6.566441743448419</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.383479100776329</v>
       </c>
       <c r="E51">
-        <v>-14.16454346971559</v>
+        <v>-14.37017694592989</v>
       </c>
       <c r="F51">
-        <v>3.881854973981482</v>
+        <v>3.911025253237961</v>
       </c>
       <c r="G51">
-        <v>-6.737901518018353</v>
+        <v>-6.13822598848923</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.541275627609674</v>
       </c>
       <c r="E52">
-        <v>-13.35859736514847</v>
+        <v>-15.03039222845617</v>
       </c>
       <c r="F52">
-        <v>3.564488227056994</v>
+        <v>3.843412096590105</v>
       </c>
       <c r="G52">
-        <v>-7.028537621456509</v>
+        <v>-6.347329976386217</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.66983868882729</v>
       </c>
       <c r="E53">
-        <v>-13.2372297332689</v>
+        <v>-14.66989852660156</v>
       </c>
       <c r="F53">
-        <v>3.799640048793274</v>
+        <v>3.814602902282346</v>
       </c>
       <c r="G53">
-        <v>-6.611458541691428</v>
+        <v>-6.170517049679281</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.767105992975209</v>
       </c>
       <c r="E54">
-        <v>-11.90774222020101</v>
+        <v>-13.27828035014843</v>
       </c>
       <c r="F54">
-        <v>4.169117055159382</v>
+        <v>4.024599139257786</v>
       </c>
       <c r="G54">
-        <v>-7.432473835430684</v>
+        <v>-7.016235634232578</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.835084266982103</v>
       </c>
       <c r="E55">
-        <v>-12.44499584799701</v>
+        <v>-12.77161656427424</v>
       </c>
       <c r="F55">
-        <v>3.593612578841926</v>
+        <v>4.230032719490844</v>
       </c>
       <c r="G55">
-        <v>-7.091136727058588</v>
+        <v>-6.499658108284701</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.875926545529623</v>
       </c>
       <c r="E56">
-        <v>-12.1781962733611</v>
+        <v>-12.07842493402411</v>
       </c>
       <c r="F56">
-        <v>3.834784066762791</v>
+        <v>4.035265398598271</v>
       </c>
       <c r="G56">
-        <v>-7.272289778967507</v>
+        <v>-6.784527241393448</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.893815752131944</v>
       </c>
       <c r="E57">
-        <v>-11.07160025095074</v>
+        <v>-11.00688835738113</v>
       </c>
       <c r="F57">
-        <v>4.203880983709193</v>
+        <v>4.023376518291067</v>
       </c>
       <c r="G57">
-        <v>-7.701223922308718</v>
+        <v>-7.000493990193343</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.894468272484081</v>
       </c>
       <c r="E58">
-        <v>-11.12129572471092</v>
+        <v>-12.24306213504697</v>
       </c>
       <c r="F58">
-        <v>3.753151945351465</v>
+        <v>4.184358640889571</v>
       </c>
       <c r="G58">
-        <v>-7.774916666012895</v>
+        <v>-5.7602576937251</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.881649935372077</v>
       </c>
       <c r="E59">
-        <v>-11.90600328618206</v>
+        <v>-9.860061371886632</v>
       </c>
       <c r="F59">
-        <v>3.951962467446156</v>
+        <v>3.878461092204696</v>
       </c>
       <c r="G59">
-        <v>-7.14109285924619</v>
+        <v>-8.109417497846394</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.858190414549343</v>
       </c>
       <c r="E60">
-        <v>-11.10338108153657</v>
+        <v>-9.917432609089808</v>
       </c>
       <c r="F60">
-        <v>3.51461257666206</v>
+        <v>3.726578943796306</v>
       </c>
       <c r="G60">
-        <v>-7.911748134242051</v>
+        <v>-7.38243162905906</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.824236200199865</v>
       </c>
       <c r="E61">
-        <v>-10.10801343770262</v>
+        <v>-9.510250340216119</v>
       </c>
       <c r="F61">
-        <v>3.985837936977406</v>
+        <v>4.018074270886175</v>
       </c>
       <c r="G61">
-        <v>-8.057216815783168</v>
+        <v>-7.761383155848354</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.779768682866914</v>
       </c>
       <c r="E62">
-        <v>-9.428955174830421</v>
+        <v>-10.19044977853825</v>
       </c>
       <c r="F62">
-        <v>3.986653545523857</v>
+        <v>4.255815451794199</v>
       </c>
       <c r="G62">
-        <v>-7.822502447594379</v>
+        <v>-7.616017101218956</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.725868139906701</v>
       </c>
       <c r="E63">
-        <v>-9.468946128792158</v>
+        <v>-10.76736831016743</v>
       </c>
       <c r="F63">
-        <v>3.696317491164089</v>
+        <v>3.710292112161927</v>
       </c>
       <c r="G63">
-        <v>-8.014679616149071</v>
+        <v>-8.554123080136693</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.6637593996988</v>
       </c>
       <c r="E64">
-        <v>-9.044360934306994</v>
+        <v>-8.735541649353912</v>
       </c>
       <c r="F64">
-        <v>3.735707424692899</v>
+        <v>3.956789603076415</v>
       </c>
       <c r="G64">
-        <v>-8.300316795822928</v>
+        <v>-7.032824777929865</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.596790348444907</v>
       </c>
       <c r="E65">
-        <v>-8.41912811348997</v>
+        <v>-9.678179741842559</v>
       </c>
       <c r="F65">
-        <v>3.723530309909085</v>
+        <v>3.555119022861254</v>
       </c>
       <c r="G65">
-        <v>-7.869379772430459</v>
+        <v>-7.861715859507046</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.528247850430248</v>
       </c>
       <c r="E66">
-        <v>-8.839565225784108</v>
+        <v>-10.60049404298478</v>
       </c>
       <c r="F66">
-        <v>3.470930800102409</v>
+        <v>3.574885256391854</v>
       </c>
       <c r="G66">
-        <v>-8.031242275482045</v>
+        <v>-7.731588245994914</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.462078557768335</v>
       </c>
       <c r="E67">
-        <v>-9.260233290252639</v>
+        <v>-8.946686278435552</v>
       </c>
       <c r="F67">
-        <v>3.820684332997633</v>
+        <v>3.534233109248439</v>
       </c>
       <c r="G67">
-        <v>-8.561359932685541</v>
+        <v>-7.117419148094863</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.400985473911576</v>
       </c>
       <c r="E68">
-        <v>-8.581315410074684</v>
+        <v>-9.040326063966159</v>
       </c>
       <c r="F68">
-        <v>3.13336388422649</v>
+        <v>3.324949539934947</v>
       </c>
       <c r="G68">
-        <v>-8.75958877848602</v>
+        <v>-6.986751915659829</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.343884332670759</v>
       </c>
       <c r="E69">
-        <v>-8.759818798509034</v>
+        <v>-9.357070178432663</v>
       </c>
       <c r="F69">
-        <v>3.244080764774862</v>
+        <v>3.496542492166895</v>
       </c>
       <c r="G69">
-        <v>-8.37948187130352</v>
+        <v>-7.632106352539815</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.289759936015888</v>
       </c>
       <c r="E70">
-        <v>-8.62807190420388</v>
+        <v>-9.182823555565522</v>
       </c>
       <c r="F70">
-        <v>3.39990475720678</v>
+        <v>3.159813356720245</v>
       </c>
       <c r="G70">
-        <v>-8.536610294233949</v>
+        <v>-7.622310448289111</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.235158198681216</v>
       </c>
       <c r="E71">
-        <v>-8.618675320637964</v>
+        <v>-9.477020397947834</v>
       </c>
       <c r="F71">
-        <v>3.448008240682338</v>
+        <v>3.444406893430629</v>
       </c>
       <c r="G71">
-        <v>-8.011653777526178</v>
+        <v>-7.789145390740682</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.175469226729226</v>
       </c>
       <c r="E72">
-        <v>-8.889147487694093</v>
+        <v>-8.875870001903602</v>
       </c>
       <c r="F72">
-        <v>3.419366919201616</v>
+        <v>3.247278267018134</v>
       </c>
       <c r="G72">
-        <v>-8.598633364912194</v>
+        <v>-7.6629672580569</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.10615102810178</v>
       </c>
       <c r="E73">
-        <v>-8.54751940855544</v>
+        <v>-9.911359925445522</v>
       </c>
       <c r="F73">
-        <v>3.233930793562811</v>
+        <v>3.005332346904619</v>
       </c>
       <c r="G73">
-        <v>-7.967312330573179</v>
+        <v>-7.638489084339529</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.020212738477065</v>
       </c>
       <c r="E74">
-        <v>-8.668271167969969</v>
+        <v>-9.703308244111122</v>
       </c>
       <c r="F74">
-        <v>2.99392808060754</v>
+        <v>2.947604682580936</v>
       </c>
       <c r="G74">
-        <v>-8.368265743016469</v>
+        <v>-7.623257264313342</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.91325248592604</v>
       </c>
       <c r="E75">
-        <v>-9.300106503890177</v>
+        <v>-9.351980173648041</v>
       </c>
       <c r="F75">
-        <v>2.899048259213563</v>
+        <v>3.107375270154129</v>
       </c>
       <c r="G75">
-        <v>-8.034840838483232</v>
+        <v>-6.474590657461341</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.7799578507800671</v>
       </c>
       <c r="E76">
-        <v>-9.667225363218005</v>
+        <v>-9.980731618769024</v>
       </c>
       <c r="F76">
-        <v>2.684313574139128</v>
+        <v>2.667812942206164</v>
       </c>
       <c r="G76">
-        <v>-7.144714596066153</v>
+        <v>-6.327926868980548</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.6151812485999181</v>
       </c>
       <c r="E77">
-        <v>-10.16867234703536</v>
+        <v>-10.61483572016707</v>
       </c>
       <c r="F77">
-        <v>2.82155752877111</v>
+        <v>3.145675614013117</v>
       </c>
       <c r="G77">
-        <v>-7.233947040531668</v>
+        <v>-6.650890449609688</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.4181962010958589</v>
       </c>
       <c r="E78">
-        <v>-10.24036261905079</v>
+        <v>-11.15173159851647</v>
       </c>
       <c r="F78">
-        <v>2.742779245419406</v>
+        <v>2.725641963708436</v>
       </c>
       <c r="G78">
-        <v>-7.172675463690838</v>
+        <v>-6.623598312183936</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.1861779021497887</v>
       </c>
       <c r="E79">
-        <v>-10.44227821810479</v>
+        <v>-11.71856069005657</v>
       </c>
       <c r="F79">
-        <v>2.553087701985815</v>
+        <v>2.445585744445785</v>
       </c>
       <c r="G79">
-        <v>-7.128135384005483</v>
+        <v>-6.58170004783892</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.08003033626631832</v>
       </c>
       <c r="E80">
-        <v>-11.31401852152935</v>
+        <v>-11.8322842578112</v>
       </c>
       <c r="F80">
-        <v>2.415469992757789</v>
+        <v>2.721017542435352</v>
       </c>
       <c r="G80">
-        <v>-7.115783738598462</v>
+        <v>-6.564293199393433</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.3780328744074549</v>
       </c>
       <c r="E81">
-        <v>-12.77244527501765</v>
+        <v>-11.82367562872261</v>
       </c>
       <c r="F81">
-        <v>2.520053180295664</v>
+        <v>2.101824954734584</v>
       </c>
       <c r="G81">
-        <v>-7.037419815138374</v>
+        <v>-5.48771372165906</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.7057942102051928</v>
       </c>
       <c r="E82">
-        <v>-13.63040090356286</v>
+        <v>-12.6136633908867</v>
       </c>
       <c r="F82">
-        <v>2.478499904486363</v>
+        <v>2.536549061110881</v>
       </c>
       <c r="G82">
-        <v>-7.009571506062025</v>
+        <v>-5.883131901960689</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.054437807046873</v>
       </c>
       <c r="E83">
-        <v>-13.74916013441401</v>
+        <v>-13.32273185100772</v>
       </c>
       <c r="F83">
-        <v>2.383715105447313</v>
+        <v>2.232277978401162</v>
       </c>
       <c r="G83">
-        <v>-6.119700175651469</v>
+        <v>-5.303753327132839</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.413550422981254</v>
       </c>
       <c r="E84">
-        <v>-14.20133732102791</v>
+        <v>-15.92368806815724</v>
       </c>
       <c r="F84">
-        <v>2.171865932550809</v>
+        <v>2.208744108497732</v>
       </c>
       <c r="G84">
-        <v>-6.147366404723158</v>
+        <v>-6.18211058015781</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.769344094541494</v>
       </c>
       <c r="E85">
-        <v>-15.37917529652694</v>
+        <v>-15.4812289867638</v>
       </c>
       <c r="F85">
-        <v>1.943777439197389</v>
+        <v>2.440688925755247</v>
       </c>
       <c r="G85">
-        <v>-6.207005882613129</v>
+        <v>-5.555387893572842</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.103920773079941</v>
       </c>
       <c r="E86">
-        <v>-16.83854397260883</v>
+        <v>-16.51516111524708</v>
       </c>
       <c r="F86">
-        <v>1.880565401288538</v>
+        <v>2.04114209517269</v>
       </c>
       <c r="G86">
-        <v>-5.130823670343469</v>
+        <v>-5.318716992970344</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.403283322918507</v>
       </c>
       <c r="E87">
-        <v>-18.24023800372903</v>
+        <v>-19.2827244196128</v>
       </c>
       <c r="F87">
-        <v>1.904121443074785</v>
+        <v>1.823974837812141</v>
       </c>
       <c r="G87">
-        <v>-4.953805489813099</v>
+        <v>-4.896824379991163</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.653388096205572</v>
       </c>
       <c r="E88">
-        <v>-19.64106709631376</v>
+        <v>-20.56345838151411</v>
       </c>
       <c r="F88">
-        <v>2.048276690321745</v>
+        <v>1.808471940605904</v>
       </c>
       <c r="G88">
-        <v>-5.003165723803633</v>
+        <v>-3.925801646776453</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.844576845248375</v>
       </c>
       <c r="E89">
-        <v>-21.23431557795842</v>
+        <v>-20.48742530292533</v>
       </c>
       <c r="F89">
-        <v>2.005161880479822</v>
+        <v>1.337009024403242</v>
       </c>
       <c r="G89">
-        <v>-4.435463443092792</v>
+        <v>-4.015689579258744</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.97212766013638</v>
       </c>
       <c r="E90">
-        <v>-22.26755484991852</v>
+        <v>-23.33243456977022</v>
       </c>
       <c r="F90">
-        <v>1.694617738639047</v>
+        <v>1.70477404467476</v>
       </c>
       <c r="G90">
-        <v>-4.637191535528282</v>
+        <v>-4.29792682866377</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.033087739438316</v>
       </c>
       <c r="E91">
-        <v>-24.63677999514753</v>
+        <v>-24.14993734000491</v>
       </c>
       <c r="F91">
-        <v>1.507583653731563</v>
+        <v>1.313983524098668</v>
       </c>
       <c r="G91">
-        <v>-4.591075636166233</v>
+        <v>-3.879692368505484</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.029372872578298</v>
       </c>
       <c r="E92">
-        <v>-26.46545931197696</v>
+        <v>-26.75248305153112</v>
       </c>
       <c r="F92">
-        <v>1.392867915746707</v>
+        <v>1.08456788518811</v>
       </c>
       <c r="G92">
-        <v>-4.643471640416279</v>
+        <v>-3.455690938017788</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.965295918673524</v>
       </c>
       <c r="E93">
-        <v>-28.55422700496293</v>
+        <v>-28.05284341978168</v>
       </c>
       <c r="F93">
-        <v>1.115915760078318</v>
+        <v>1.153069500854528</v>
       </c>
       <c r="G93">
-        <v>-4.491199787791961</v>
+        <v>-3.390582438896941</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.848216363509315</v>
       </c>
       <c r="E94">
-        <v>-30.57899151056148</v>
+        <v>-30.91013164389837</v>
       </c>
       <c r="F94">
-        <v>0.9524503866044046</v>
+        <v>0.919879890747477</v>
       </c>
       <c r="G94">
-        <v>-4.462139819048239</v>
+        <v>-3.537861988848038</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.690024068508369</v>
       </c>
       <c r="E95">
-        <v>-32.5037786312557</v>
+        <v>-31.70332556565989</v>
       </c>
       <c r="F95">
-        <v>0.8727662234690688</v>
+        <v>0.7282752305680354</v>
       </c>
       <c r="G95">
-        <v>-4.326109502839586</v>
+        <v>-3.703912332006802</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.498913630377927</v>
       </c>
       <c r="E96">
-        <v>-34.9070624294964</v>
+        <v>-35.1171813592153</v>
       </c>
       <c r="F96">
-        <v>0.8049503524640363</v>
+        <v>0.2547732929992454</v>
       </c>
       <c r="G96">
-        <v>-4.684535647285399</v>
+        <v>-3.301892923899866</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.290611806574836</v>
       </c>
       <c r="E97">
-        <v>-36.81740145386915</v>
+        <v>-37.24790762811934</v>
       </c>
       <c r="F97">
-        <v>0.3796049525189713</v>
+        <v>1.040675475741705</v>
       </c>
       <c r="G97">
-        <v>-4.874001479043428</v>
+        <v>-3.392241022212116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.065773215099008</v>
       </c>
       <c r="E98">
-        <v>-40.19969378359109</v>
+        <v>-39.2971191006483</v>
       </c>
       <c r="F98">
-        <v>0.5262933373776769</v>
+        <v>0.4225851473580824</v>
       </c>
       <c r="G98">
-        <v>-4.759761173574258</v>
+        <v>-3.80567188079292</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.843568766664264</v>
       </c>
       <c r="E99">
-        <v>-42.42615878572829</v>
+        <v>-42.26302730231298</v>
       </c>
       <c r="F99">
-        <v>0.1392823309687814</v>
+        <v>0.6529161682877648</v>
       </c>
       <c r="G99">
-        <v>-5.161356831852167</v>
+        <v>-3.379300099699105</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.609789166969947</v>
       </c>
       <c r="E100">
-        <v>-45.47989221229772</v>
+        <v>-44.80816328460694</v>
       </c>
       <c r="F100">
-        <v>0.339876897777215</v>
+        <v>-0.3654566220761363</v>
       </c>
       <c r="G100">
-        <v>-4.715479316440967</v>
+        <v>-4.640800030166087</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.393422147973446</v>
       </c>
       <c r="E101">
-        <v>-47.46705000549958</v>
+        <v>-47.0447562188623</v>
       </c>
       <c r="F101">
-        <v>0.0007912079283903522</v>
+        <v>-0.3413256950425854</v>
       </c>
       <c r="G101">
-        <v>-5.515869911470562</v>
+        <v>-4.308960876946161</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.138985568000148</v>
       </c>
       <c r="E102">
-        <v>-49.9939158594096</v>
+        <v>-50.4196410972262</v>
       </c>
       <c r="F102">
-        <v>-0.2993899542547065</v>
+        <v>-0.4165224274665235</v>
       </c>
       <c r="G102">
-        <v>-5.45019199851696</v>
+        <v>-3.4699891842019</v>
       </c>
     </row>
   </sheetData>
